--- a/RouteBook/Routebook.xlsx
+++ b/RouteBook/Routebook.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17580"/>
+    <workbookView windowHeight="16980"/>
   </bookViews>
   <sheets>
     <sheet name="Route Optimizer Export" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="608">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="623">
   <si>
     <t>City</t>
   </si>
@@ -1035,6 +1035,51 @@
   </si>
   <si>
     <t>1603 S Main Ave, Rugby, ND 58368</t>
+  </si>
+  <si>
+    <t>Dale and Martha Hawk Museum</t>
+  </si>
+  <si>
+    <t>4839 78th St NE, Wolford, ND 58385</t>
+  </si>
+  <si>
+    <t>Starion Bank Dunseith</t>
+  </si>
+  <si>
+    <t>11 Main St NE, Dunseith, ND 58329</t>
+  </si>
+  <si>
+    <t>Cassavant Insurance</t>
+  </si>
+  <si>
+    <t>710 1st Ave Rolette, ND 58366</t>
+  </si>
+  <si>
+    <t>703 1st St N Rugby, ND 58368</t>
+  </si>
+  <si>
+    <t>Rugby Golf Club</t>
+  </si>
+  <si>
+    <t>6520 30th Ave NE Rugby, ND 58368</t>
+  </si>
+  <si>
+    <t>Rugby Home Sales / Rugby Homes &amp; RV Center</t>
+  </si>
+  <si>
+    <t>1040 ND-3 S Rugby, ND 58368</t>
+  </si>
+  <si>
+    <t>Home Town Liquor</t>
+  </si>
+  <si>
+    <t>605 US-2, Rugby, ND 58368</t>
+  </si>
+  <si>
+    <t>LA Bella Vita Salon</t>
+  </si>
+  <si>
+    <t>101 US-2, Rugby, ND 58368</t>
   </si>
   <si>
     <t>Aberdeen</t>
@@ -3025,12 +3070,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F301"/>
+  <dimension ref="A1:F309"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="30.1428571428571" customWidth="1"/>
-    <col min="2" max="2" width="43.1428571428571" customWidth="1"/>
-    <col min="3" max="3" width="51.1428571428571" customWidth="1"/>
+    <col min="2" max="2" width="89.7142857142857" customWidth="1"/>
+    <col min="3" max="3" width="78.2857142857143" customWidth="1"/>
     <col min="4" max="4" width="78.1428571428571" customWidth="1"/>
     <col min="5" max="5" width="8.42857142857143" customWidth="1"/>
   </cols>
@@ -5037,321 +5082,313 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B158" t="s">
         <v>336</v>
       </c>
-      <c r="B158" s="1" t="s">
+      <c r="C158" t="s">
         <v>337</v>
       </c>
-      <c r="C158" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="D158" s="1"/>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B159" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B159" t="s">
+        <v>338</v>
+      </c>
+      <c r="C159" t="s">
         <v>339</v>
-      </c>
-      <c r="C159" s="1" t="s">
-        <v>340</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B160" s="1" t="s">
-        <v>342</v>
-      </c>
-      <c r="C160" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D160" s="1"/>
+        <v>180</v>
+      </c>
+      <c r="B160" t="s">
+        <v>340</v>
+      </c>
+      <c r="C160" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="C161" s="1" t="s">
-        <v>345</v>
-      </c>
-      <c r="D161" s="1"/>
+        <v>180</v>
+      </c>
+      <c r="B161" t="s">
+        <v>107</v>
+      </c>
+      <c r="C161" t="s">
+        <v>342</v>
+      </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B162" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="D162" s="1"/>
+        <v>180</v>
+      </c>
+      <c r="B162" t="s">
+        <v>343</v>
+      </c>
+      <c r="C162" t="s">
+        <v>344</v>
+      </c>
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="C163" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="D163" s="1"/>
+        <v>180</v>
+      </c>
+      <c r="B163" t="s">
+        <v>345</v>
+      </c>
+      <c r="C163" t="s">
+        <v>346</v>
+      </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="C164" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="D164" s="1"/>
+        <v>180</v>
+      </c>
+      <c r="B164" t="s">
+        <v>347</v>
+      </c>
+      <c r="C164" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="D165" s="1"/>
+        <v>180</v>
+      </c>
+      <c r="B165" t="s">
+        <v>349</v>
+      </c>
+      <c r="C165" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D166" s="1"/>
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B167" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>356</v>
       </c>
-      <c r="C167" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="D167" s="1"/>
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B168" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="C168" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="C168" s="1" t="s">
-        <v>359</v>
       </c>
       <c r="D168" s="1"/>
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B169" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="C169" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="C169" s="1" t="s">
-        <v>361</v>
       </c>
       <c r="D169" s="1"/>
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B170" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="C170" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="C170" s="1" t="s">
-        <v>363</v>
       </c>
       <c r="D170" s="1"/>
     </row>
     <row r="171" spans="1:4">
       <c r="A171" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B171" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="C171" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>365</v>
       </c>
       <c r="D171" s="1"/>
     </row>
     <row r="172" spans="1:4">
       <c r="A172" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B172" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C172" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="C172" s="1" t="s">
-        <v>367</v>
       </c>
       <c r="D172" s="1"/>
     </row>
     <row r="173" spans="1:4">
       <c r="A173" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B173" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C173" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="C173" s="1" t="s">
-        <v>369</v>
       </c>
       <c r="D173" s="1"/>
     </row>
     <row r="174" spans="1:4">
       <c r="A174" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B174" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C174" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="C174" s="1" t="s">
-        <v>371</v>
       </c>
       <c r="D174" s="1"/>
     </row>
     <row r="175" spans="1:4">
       <c r="A175" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B175" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C175" s="1" t="s">
         <v>372</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>373</v>
       </c>
       <c r="D175" s="1"/>
     </row>
     <row r="176" spans="1:4">
       <c r="A176" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B176" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C176" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="C176" s="1" t="s">
-        <v>375</v>
       </c>
       <c r="D176" s="1"/>
     </row>
     <row r="177" spans="1:4">
       <c r="A177" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B177" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C177" s="1" t="s">
         <v>376</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>377</v>
       </c>
       <c r="D177" s="1"/>
     </row>
     <row r="178" spans="1:4">
       <c r="A178" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B178" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C178" s="1" t="s">
         <v>378</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>379</v>
       </c>
       <c r="D178" s="1"/>
     </row>
     <row r="179" spans="1:4">
       <c r="A179" s="1" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>170</v>
+        <v>379</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>171</v>
+        <v>380</v>
       </c>
       <c r="D179" s="1"/>
     </row>
     <row r="180" spans="1:4">
       <c r="A180" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B180" t="s">
-        <v>380</v>
-      </c>
-      <c r="C180" t="s">
+        <v>351</v>
+      </c>
+      <c r="B180" s="1" t="s">
         <v>381</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>382</v>
       </c>
       <c r="D180" s="1"/>
     </row>
     <row r="181" spans="1:4">
       <c r="A181" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B181" t="s">
-        <v>382</v>
-      </c>
-      <c r="C181" t="s">
+        <v>351</v>
+      </c>
+      <c r="B181" s="1" t="s">
         <v>383</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="D181" s="1"/>
     </row>
     <row r="182" spans="1:4">
       <c r="A182" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B182" t="s">
-        <v>384</v>
-      </c>
-      <c r="C182" t="s">
+        <v>351</v>
+      </c>
+      <c r="B182" s="1" t="s">
         <v>385</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>386</v>
       </c>
       <c r="D182" s="1"/>
     </row>
     <row r="183" spans="1:4">
       <c r="A183" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="B183" t="s">
-        <v>386</v>
-      </c>
-      <c r="C183" t="s">
+        <v>351</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>387</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>388</v>
       </c>
       <c r="D183" s="1"/>
     </row>
     <row r="184" spans="1:4">
       <c r="A184" s="1" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>389</v>
@@ -5363,90 +5400,91 @@
     </row>
     <row r="185" spans="1:4">
       <c r="A185" s="1" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>391</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D185" s="1"/>
     </row>
     <row r="186" spans="1:4">
       <c r="A186" s="1" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D186" s="1"/>
     </row>
     <row r="187" spans="1:4">
       <c r="A187" s="1" t="s">
-        <v>388</v>
+        <v>351</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>394</v>
+        <v>170</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>395</v>
+        <v>171</v>
       </c>
       <c r="D187" s="1"/>
     </row>
     <row r="188" spans="1:4">
       <c r="A188" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B188" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B188" t="s">
+        <v>395</v>
+      </c>
+      <c r="C188" t="s">
         <v>396</v>
-      </c>
-      <c r="C188" s="1" t="s">
-        <v>397</v>
       </c>
       <c r="D188" s="1"/>
     </row>
     <row r="189" spans="1:4">
       <c r="A189" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B189" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B189" t="s">
+        <v>397</v>
+      </c>
+      <c r="C189" t="s">
         <v>398</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>399</v>
       </c>
       <c r="D189" s="1"/>
     </row>
     <row r="190" spans="1:4">
       <c r="A190" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B190" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B190" t="s">
+        <v>399</v>
+      </c>
+      <c r="C190" t="s">
         <v>400</v>
-      </c>
-      <c r="C190" s="1" t="s">
-        <v>401</v>
       </c>
       <c r="D190" s="1"/>
     </row>
     <row r="191" spans="1:4">
       <c r="A191" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B191" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B191" t="s">
+        <v>401</v>
+      </c>
+      <c r="C191" t="s">
         <v>402</v>
       </c>
-      <c r="C191" s="1" t="s">
-        <v>403</v>
-      </c>
+      <c r="D191" s="1"/>
     </row>
     <row r="192" spans="1:4">
       <c r="A192" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>404</v>
@@ -5458,41 +5496,43 @@
     </row>
     <row r="193" spans="1:4">
       <c r="A193" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>406</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="D193" s="1"/>
     </row>
     <row r="194" spans="1:4">
       <c r="A194" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B194" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C194" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="C194" s="1" t="s">
-        <v>409</v>
       </c>
       <c r="D194" s="1"/>
     </row>
     <row r="195" spans="1:4">
       <c r="A195" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B195" s="1"/>
+        <v>403</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>409</v>
+      </c>
       <c r="C195" s="1" t="s">
         <v>410</v>
       </c>
       <c r="D195" s="1"/>
     </row>
-    <row r="196" ht="28.5" spans="1:4">
+    <row r="196" spans="1:4">
       <c r="A196" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>411</v>
@@ -5500,109 +5540,106 @@
       <c r="C196" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="D196" s="3" t="s">
-        <v>413</v>
-      </c>
+      <c r="D196" s="1"/>
     </row>
     <row r="197" spans="1:4">
       <c r="A197" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B197" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C197" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="C197" s="1" t="s">
-        <v>415</v>
       </c>
       <c r="D197" s="1"/>
     </row>
     <row r="198" spans="1:4">
       <c r="A198" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B198" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C198" s="1" t="s">
         <v>416</v>
-      </c>
-      <c r="C198" s="1" t="s">
-        <v>417</v>
       </c>
       <c r="D198" s="1"/>
     </row>
     <row r="199" spans="1:4">
       <c r="A199" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B199" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="C199" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="C199" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="D199" s="1"/>
     </row>
     <row r="200" spans="1:4">
       <c r="A200" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B200" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C200" s="1" t="s">
         <v>420</v>
-      </c>
-      <c r="C200" s="1" t="s">
-        <v>421</v>
       </c>
       <c r="D200" s="1"/>
     </row>
     <row r="201" spans="1:4">
       <c r="A201" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B201" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="C201" s="1" t="s">
         <v>422</v>
-      </c>
-      <c r="C201" s="1" t="s">
-        <v>423</v>
       </c>
       <c r="D201" s="1"/>
     </row>
     <row r="202" spans="1:4">
       <c r="A202" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B202" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="C202" s="1" t="s">
         <v>424</v>
-      </c>
-      <c r="C202" s="1" t="s">
-        <v>425</v>
       </c>
       <c r="D202" s="1"/>
     </row>
     <row r="203" spans="1:4">
       <c r="A203" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B203" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B203" s="1"/>
+      <c r="C203" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="D203" s="1"/>
+    </row>
+    <row r="204" ht="28.5" spans="1:4">
+      <c r="A204" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B204" s="1" t="s">
         <v>426</v>
       </c>
-      <c r="C203" s="1" t="s">
+      <c r="C204" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="D203" s="1"/>
-    </row>
-    <row r="204" spans="1:4">
-      <c r="A204" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="B204" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C204" s="1" t="s">
+      <c r="D204" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="D204" s="1"/>
     </row>
     <row r="205" spans="1:4">
       <c r="A205" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>429</v>
@@ -5614,7 +5651,7 @@
     </row>
     <row r="206" spans="1:4">
       <c r="A206" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>431</v>
@@ -5626,7 +5663,7 @@
     </row>
     <row r="207" spans="1:4">
       <c r="A207" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>433</v>
@@ -5638,7 +5675,7 @@
     </row>
     <row r="208" spans="1:4">
       <c r="A208" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>435</v>
@@ -5650,7 +5687,7 @@
     </row>
     <row r="209" spans="1:4">
       <c r="A209" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>437</v>
@@ -5662,7 +5699,7 @@
     </row>
     <row r="210" spans="1:4">
       <c r="A210" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>439</v>
@@ -5674,7 +5711,7 @@
     </row>
     <row r="211" spans="1:4">
       <c r="A211" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>441</v>
@@ -5686,82 +5723,82 @@
     </row>
     <row r="212" spans="1:4">
       <c r="A212" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B212" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C212" s="1" t="s">
         <v>443</v>
-      </c>
-      <c r="C212" s="1" t="s">
-        <v>444</v>
       </c>
       <c r="D212" s="1"/>
     </row>
     <row r="213" spans="1:4">
       <c r="A213" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B213" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="C213" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="C213" s="1" t="s">
-        <v>446</v>
       </c>
       <c r="D213" s="1"/>
     </row>
     <row r="214" spans="1:4">
       <c r="A214" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B214" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="C214" s="1" t="s">
         <v>447</v>
-      </c>
-      <c r="C214" s="1" t="s">
-        <v>448</v>
       </c>
       <c r="D214" s="1"/>
     </row>
     <row r="215" spans="1:4">
       <c r="A215" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B215" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C215" s="1" t="s">
         <v>449</v>
-      </c>
-      <c r="C215" s="1" t="s">
-        <v>450</v>
       </c>
       <c r="D215" s="1"/>
     </row>
     <row r="216" spans="1:4">
       <c r="A216" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B216" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="C216" s="1" t="s">
         <v>451</v>
-      </c>
-      <c r="C216" s="1" t="s">
-        <v>452</v>
       </c>
       <c r="D216" s="1"/>
     </row>
     <row r="217" spans="1:4">
       <c r="A217" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B217" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="C217" s="1" t="s">
         <v>453</v>
-      </c>
-      <c r="C217" s="1" t="s">
-        <v>454</v>
       </c>
       <c r="D217" s="1"/>
     </row>
     <row r="218" spans="1:4">
       <c r="A218" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B218" s="1" t="s">
-        <v>204</v>
+        <v>454</v>
       </c>
       <c r="C218" s="1" t="s">
         <v>455</v>
@@ -5770,388 +5807,396 @@
     </row>
     <row r="219" spans="1:4">
       <c r="A219" s="1" t="s">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="B219" s="1" t="s">
-        <v>170</v>
+        <v>456</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>171</v>
+        <v>457</v>
       </c>
       <c r="D219" s="1"/>
     </row>
     <row r="220" spans="1:4">
       <c r="A220" s="1" t="s">
-        <v>456</v>
+        <v>403</v>
       </c>
       <c r="B220" s="1" t="s">
-        <v>352</v>
+        <v>458</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="D220" s="1"/>
     </row>
     <row r="221" spans="1:4">
       <c r="A221" s="1" t="s">
-        <v>456</v>
+        <v>403</v>
       </c>
       <c r="B221" s="1" t="s">
-        <v>116</v>
+        <v>460</v>
       </c>
       <c r="C221" s="1" t="s">
-        <v>117</v>
+        <v>461</v>
       </c>
       <c r="D221" s="1"/>
     </row>
     <row r="222" spans="1:4">
       <c r="A222" s="1" t="s">
-        <v>456</v>
+        <v>403</v>
       </c>
       <c r="B222" s="1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="C222" s="1" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="D222" s="1"/>
     </row>
     <row r="223" spans="1:4">
       <c r="A223" s="1" t="s">
-        <v>456</v>
+        <v>403</v>
       </c>
       <c r="B223" s="1" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C223" s="1" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D223" s="1"/>
     </row>
     <row r="224" spans="1:4">
       <c r="A224" s="1" t="s">
-        <v>456</v>
+        <v>403</v>
       </c>
       <c r="B224" s="1" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C224" s="1" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D224" s="1"/>
     </row>
     <row r="225" spans="1:4">
       <c r="A225" s="1" t="s">
-        <v>456</v>
+        <v>403</v>
       </c>
       <c r="B225" s="1" t="s">
-        <v>344</v>
+        <v>468</v>
       </c>
       <c r="C225" s="1" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="D225" s="1"/>
     </row>
     <row r="226" spans="1:4">
       <c r="A226" s="1" t="s">
-        <v>456</v>
+        <v>403</v>
       </c>
       <c r="B226" s="1" t="s">
-        <v>465</v>
+        <v>204</v>
       </c>
       <c r="C226" s="1" t="s">
-        <v>466</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="D226" s="1"/>
     </row>
     <row r="227" spans="1:4">
       <c r="A227" s="1" t="s">
-        <v>456</v>
+        <v>403</v>
       </c>
       <c r="B227" s="1" t="s">
-        <v>467</v>
+        <v>170</v>
       </c>
       <c r="C227" s="1" t="s">
-        <v>468</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="D227" s="1"/>
     </row>
     <row r="228" spans="1:4">
       <c r="A228" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B228" s="1" t="s">
-        <v>5</v>
+        <v>367</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>6</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="D228" s="1"/>
     </row>
     <row r="229" spans="1:4">
       <c r="A229" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>469</v>
+        <v>116</v>
       </c>
       <c r="C229" s="1" t="s">
-        <v>470</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="D229" s="1"/>
     </row>
     <row r="230" spans="1:4">
       <c r="A230" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B230" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C230" s="1" t="s">
-        <v>472</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="D230" s="1"/>
     </row>
     <row r="231" spans="1:4">
       <c r="A231" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B231" s="1" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C231" s="1" t="s">
-        <v>474</v>
-      </c>
+        <v>476</v>
+      </c>
+      <c r="D231" s="1"/>
     </row>
     <row r="232" spans="1:4">
       <c r="A232" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B232" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C232" s="1" t="s">
-        <v>476</v>
-      </c>
+        <v>478</v>
+      </c>
+      <c r="D232" s="1"/>
     </row>
     <row r="233" spans="1:4">
       <c r="A233" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B233" s="1" t="s">
-        <v>477</v>
+        <v>359</v>
       </c>
       <c r="C233" s="1" t="s">
-        <v>478</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="D233" s="1"/>
     </row>
     <row r="234" spans="1:4">
       <c r="A234" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B234" s="1" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C234" s="1" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="235" spans="1:4">
       <c r="A235" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B235" s="1" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C235" s="1" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="236" spans="1:4">
       <c r="A236" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B236" s="1" t="s">
-        <v>483</v>
+        <v>5</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>484</v>
+        <v>6</v>
       </c>
     </row>
     <row r="237" spans="1:4">
       <c r="A237" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B237" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C237" s="1" t="s">
         <v>485</v>
-      </c>
-      <c r="C237" s="1" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="238" spans="1:4">
       <c r="A238" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B238" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C238" s="1" t="s">
         <v>487</v>
-      </c>
-      <c r="C238" s="1" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="239" spans="1:4">
       <c r="A239" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B239" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="C239" s="1" t="s">
         <v>489</v>
-      </c>
-      <c r="C239" s="1" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="240" spans="1:4">
       <c r="A240" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B240" s="1" t="s">
-        <v>53</v>
+        <v>490</v>
       </c>
       <c r="C240" s="1" t="s">
-        <v>54</v>
+        <v>491</v>
       </c>
     </row>
     <row r="241" spans="1:3">
       <c r="A241" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B241" s="1" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C241" s="1" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="242" spans="1:3">
       <c r="A242" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B242" s="1" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C242" s="1" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="243" spans="1:3">
       <c r="A243" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B243" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C243" s="1" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="244" spans="1:3">
       <c r="A244" s="1" t="s">
-        <v>456</v>
+        <v>471</v>
       </c>
       <c r="B244" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="C244" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3">
+      <c r="A245" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B245" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C245" s="1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3">
+      <c r="A246" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B246" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="C246" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3">
+      <c r="A247" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B247" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="C247" s="1" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3">
+      <c r="A248" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B248" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C248" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3">
+      <c r="A249" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B249" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C249" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3">
+      <c r="A250" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B250" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C250" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3">
+      <c r="A251" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B251" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="C251" s="1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3">
+      <c r="A252" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="B252" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C244" s="1" t="s">
+      <c r="C252" s="1" t="s">
         <v>171</v>
-      </c>
-    </row>
-    <row r="245" spans="1:3">
-      <c r="A245" t="s">
-        <v>496</v>
-      </c>
-      <c r="B245" t="s">
-        <v>497</v>
-      </c>
-      <c r="C245" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="246" spans="1:3">
-      <c r="A246" t="s">
-        <v>496</v>
-      </c>
-      <c r="B246" t="s">
-        <v>5</v>
-      </c>
-      <c r="C246" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="247" spans="1:3">
-      <c r="A247" t="s">
-        <v>496</v>
-      </c>
-      <c r="B247" t="s">
-        <v>500</v>
-      </c>
-      <c r="C247" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="248" spans="1:3">
-      <c r="A248" t="s">
-        <v>496</v>
-      </c>
-      <c r="B248" t="s">
-        <v>502</v>
-      </c>
-      <c r="C248" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="249" spans="1:3">
-      <c r="A249" t="s">
-        <v>496</v>
-      </c>
-      <c r="B249" t="s">
-        <v>504</v>
-      </c>
-      <c r="C249" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="250" spans="1:3">
-      <c r="A250" t="s">
-        <v>496</v>
-      </c>
-      <c r="B250" t="s">
-        <v>506</v>
-      </c>
-      <c r="C250" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="251" spans="1:3">
-      <c r="A251" t="s">
-        <v>496</v>
-      </c>
-      <c r="B251" t="s">
-        <v>508</v>
-      </c>
-      <c r="C251" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="252" spans="1:3">
-      <c r="A252" t="s">
-        <v>496</v>
-      </c>
-      <c r="B252" t="s">
-        <v>510</v>
-      </c>
-      <c r="C252" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="253" spans="1:3">
       <c r="A253" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B253" t="s">
         <v>512</v>
@@ -6162,76 +6207,76 @@
     </row>
     <row r="254" spans="1:3">
       <c r="A254" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B254" t="s">
+        <v>5</v>
+      </c>
+      <c r="C254" t="s">
         <v>514</v>
-      </c>
-      <c r="C254" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="255" spans="1:3">
       <c r="A255" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B255" t="s">
+        <v>515</v>
+      </c>
+      <c r="C255" t="s">
         <v>516</v>
-      </c>
-      <c r="C255" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="256" spans="1:3">
       <c r="A256" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B256" t="s">
+        <v>517</v>
+      </c>
+      <c r="C256" t="s">
         <v>518</v>
-      </c>
-      <c r="C256" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="257" spans="1:3">
       <c r="A257" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B257" t="s">
+        <v>519</v>
+      </c>
+      <c r="C257" t="s">
         <v>520</v>
-      </c>
-      <c r="C257" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="258" spans="1:3">
       <c r="A258" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B258" t="s">
+        <v>521</v>
+      </c>
+      <c r="C258" t="s">
         <v>522</v>
-      </c>
-      <c r="C258" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="259" spans="1:3">
       <c r="A259" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B259" t="s">
+        <v>523</v>
+      </c>
+      <c r="C259" t="s">
         <v>524</v>
-      </c>
-      <c r="C259" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="260" spans="1:3">
       <c r="A260" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B260" t="s">
-        <v>344</v>
+        <v>525</v>
       </c>
       <c r="C260" t="s">
         <v>526</v>
@@ -6239,7 +6284,7 @@
     </row>
     <row r="261" spans="1:3">
       <c r="A261" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B261" t="s">
         <v>527</v>
@@ -6250,7 +6295,7 @@
     </row>
     <row r="262" spans="1:3">
       <c r="A262" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B262" t="s">
         <v>529</v>
@@ -6261,7 +6306,7 @@
     </row>
     <row r="263" spans="1:3">
       <c r="A263" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B263" t="s">
         <v>531</v>
@@ -6272,7 +6317,7 @@
     </row>
     <row r="264" spans="1:3">
       <c r="A264" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B264" t="s">
         <v>533</v>
@@ -6283,7 +6328,7 @@
     </row>
     <row r="265" spans="1:3">
       <c r="A265" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B265" t="s">
         <v>535</v>
@@ -6294,7 +6339,7 @@
     </row>
     <row r="266" spans="1:3">
       <c r="A266" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B266" t="s">
         <v>537</v>
@@ -6305,7 +6350,7 @@
     </row>
     <row r="267" spans="1:3">
       <c r="A267" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B267" t="s">
         <v>539</v>
@@ -6316,109 +6361,109 @@
     </row>
     <row r="268" spans="1:3">
       <c r="A268" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B268" t="s">
+        <v>359</v>
+      </c>
+      <c r="C268" t="s">
         <v>541</v>
-      </c>
-      <c r="C268" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B269" t="s">
+        <v>542</v>
+      </c>
+      <c r="C269" t="s">
         <v>543</v>
-      </c>
-      <c r="C269" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="270" spans="1:3">
       <c r="A270" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B270" t="s">
+        <v>544</v>
+      </c>
+      <c r="C270" t="s">
         <v>545</v>
-      </c>
-      <c r="C270" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="271" spans="1:3">
       <c r="A271" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B271" t="s">
+        <v>546</v>
+      </c>
+      <c r="C271" t="s">
         <v>547</v>
-      </c>
-      <c r="C271" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="272" spans="1:3">
       <c r="A272" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B272" t="s">
+        <v>548</v>
+      </c>
+      <c r="C272" t="s">
         <v>549</v>
-      </c>
-      <c r="C272" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="273" spans="1:3">
       <c r="A273" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B273" t="s">
+        <v>550</v>
+      </c>
+      <c r="C273" t="s">
         <v>551</v>
-      </c>
-      <c r="C273" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="274" spans="1:3">
       <c r="A274" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B274" t="s">
+        <v>552</v>
+      </c>
+      <c r="C274" t="s">
         <v>553</v>
-      </c>
-      <c r="C274" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="275" spans="1:3">
       <c r="A275" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B275" t="s">
+        <v>554</v>
+      </c>
+      <c r="C275" t="s">
         <v>555</v>
-      </c>
-      <c r="C275" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="276" spans="1:3">
       <c r="A276" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B276" t="s">
+        <v>556</v>
+      </c>
+      <c r="C276" t="s">
         <v>557</v>
-      </c>
-      <c r="C276" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="277" spans="1:3">
       <c r="A277" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B277" t="s">
-        <v>25</v>
+        <v>558</v>
       </c>
       <c r="C277" t="s">
         <v>559</v>
@@ -6426,7 +6471,7 @@
     </row>
     <row r="278" spans="1:3">
       <c r="A278" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B278" t="s">
         <v>560</v>
@@ -6437,7 +6482,7 @@
     </row>
     <row r="279" spans="1:3">
       <c r="A279" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B279" t="s">
         <v>562</v>
@@ -6448,7 +6493,7 @@
     </row>
     <row r="280" spans="1:3">
       <c r="A280" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B280" t="s">
         <v>564</v>
@@ -6459,7 +6504,7 @@
     </row>
     <row r="281" spans="1:3">
       <c r="A281" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B281" t="s">
         <v>566</v>
@@ -6470,7 +6515,7 @@
     </row>
     <row r="282" spans="1:3">
       <c r="A282" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B282" t="s">
         <v>568</v>
@@ -6481,7 +6526,7 @@
     </row>
     <row r="283" spans="1:3">
       <c r="A283" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B283" t="s">
         <v>570</v>
@@ -6492,7 +6537,7 @@
     </row>
     <row r="284" spans="1:3">
       <c r="A284" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B284" t="s">
         <v>572</v>
@@ -6503,189 +6548,277 @@
     </row>
     <row r="285" spans="1:3">
       <c r="A285" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B285" t="s">
+        <v>25</v>
+      </c>
+      <c r="C285" t="s">
         <v>574</v>
-      </c>
-      <c r="C285" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="286" spans="1:3">
       <c r="A286" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B286" t="s">
+        <v>575</v>
+      </c>
+      <c r="C286" t="s">
         <v>576</v>
-      </c>
-      <c r="C286" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B287" t="s">
+        <v>577</v>
+      </c>
+      <c r="C287" t="s">
         <v>578</v>
-      </c>
-      <c r="C287" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="288" spans="1:3">
       <c r="A288" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B288" t="s">
+        <v>579</v>
+      </c>
+      <c r="C288" t="s">
         <v>580</v>
-      </c>
-      <c r="C288" t="s">
-        <v>581</v>
       </c>
     </row>
     <row r="289" spans="1:3">
       <c r="A289" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B289" t="s">
+        <v>581</v>
+      </c>
+      <c r="C289" t="s">
         <v>582</v>
-      </c>
-      <c r="C289" t="s">
-        <v>583</v>
       </c>
     </row>
     <row r="290" spans="1:3">
       <c r="A290" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B290" t="s">
+        <v>583</v>
+      </c>
+      <c r="C290" t="s">
         <v>584</v>
-      </c>
-      <c r="C290" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="291" spans="1:3">
       <c r="A291" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B291" t="s">
+        <v>585</v>
+      </c>
+      <c r="C291" t="s">
         <v>586</v>
-      </c>
-      <c r="C291" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B292" t="s">
+        <v>587</v>
+      </c>
+      <c r="C292" t="s">
         <v>588</v>
-      </c>
-      <c r="C292" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="293" spans="1:3">
       <c r="A293" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B293" t="s">
+        <v>589</v>
+      </c>
+      <c r="C293" t="s">
         <v>590</v>
-      </c>
-      <c r="C293" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="294" spans="1:3">
       <c r="A294" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B294" t="s">
+        <v>591</v>
+      </c>
+      <c r="C294" t="s">
         <v>592</v>
-      </c>
-      <c r="C294" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="295" spans="1:3">
       <c r="A295" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B295" t="s">
+        <v>593</v>
+      </c>
+      <c r="C295" t="s">
         <v>594</v>
-      </c>
-      <c r="C295" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="296" spans="1:3">
       <c r="A296" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B296" t="s">
+        <v>595</v>
+      </c>
+      <c r="C296" t="s">
         <v>596</v>
-      </c>
-      <c r="C296" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="297" spans="1:3">
       <c r="A297" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B297" t="s">
+        <v>597</v>
+      </c>
+      <c r="C297" t="s">
         <v>598</v>
-      </c>
-      <c r="C297" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="298" spans="1:3">
       <c r="A298" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B298" t="s">
+        <v>599</v>
+      </c>
+      <c r="C298" t="s">
         <v>600</v>
-      </c>
-      <c r="C298" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="299" spans="1:3">
       <c r="A299" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B299" t="s">
+        <v>601</v>
+      </c>
+      <c r="C299" t="s">
         <v>602</v>
-      </c>
-      <c r="C299" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="300" spans="1:3">
       <c r="A300" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B300" t="s">
+        <v>603</v>
+      </c>
+      <c r="C300" t="s">
         <v>604</v>
-      </c>
-      <c r="C300" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="301" spans="1:3">
       <c r="A301" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="B301" t="s">
+        <v>605</v>
+      </c>
+      <c r="C301" t="s">
         <v>606</v>
       </c>
-      <c r="C301" t="s">
+    </row>
+    <row r="302" spans="1:3">
+      <c r="A302" t="s">
+        <v>511</v>
+      </c>
+      <c r="B302" t="s">
         <v>607</v>
+      </c>
+      <c r="C302" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3">
+      <c r="A303" t="s">
+        <v>511</v>
+      </c>
+      <c r="B303" t="s">
+        <v>609</v>
+      </c>
+      <c r="C303" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3">
+      <c r="A304" t="s">
+        <v>511</v>
+      </c>
+      <c r="B304" t="s">
+        <v>611</v>
+      </c>
+      <c r="C304" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3">
+      <c r="A305" t="s">
+        <v>511</v>
+      </c>
+      <c r="B305" t="s">
+        <v>613</v>
+      </c>
+      <c r="C305" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3">
+      <c r="A306" t="s">
+        <v>511</v>
+      </c>
+      <c r="B306" t="s">
+        <v>615</v>
+      </c>
+      <c r="C306" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3">
+      <c r="A307" t="s">
+        <v>511</v>
+      </c>
+      <c r="B307" t="s">
+        <v>617</v>
+      </c>
+      <c r="C307" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3">
+      <c r="A308" t="s">
+        <v>511</v>
+      </c>
+      <c r="B308" t="s">
+        <v>619</v>
+      </c>
+      <c r="C308" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3">
+      <c r="A309" t="s">
+        <v>511</v>
+      </c>
+      <c r="B309" t="s">
+        <v>621</v>
+      </c>
+      <c r="C309" t="s">
+        <v>622</v>
       </c>
     </row>
   </sheetData>
